--- a/data/trans_orig/P2A_fisi_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23167</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256088</t>
+          <t>257124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269432</t>
+          <t>269610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248190</t>
+          <t>248302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258738</t>
+          <t>258778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510681</t>
+          <t>510274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>526303</t>
+          <t>526374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26819</t>
+          <t>26853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52521</t>
+          <t>52965</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53520</t>
+          <t>50889</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60578</t>
+          <t>61052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95813</t>
+          <t>95916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>440554</t>
+          <t>440110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>466256</t>
+          <t>466222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450429</t>
+          <t>453060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476496</t>
+          <t>476478</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>901211</t>
+          <t>901108</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>936446</t>
+          <t>935972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17859</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>25841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305209</t>
+          <t>304184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315890</t>
+          <t>315788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>317553</t>
+          <t>318636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331004</t>
+          <t>331127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627759</t>
+          <t>628417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644105</t>
+          <t>644986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28793</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>18046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>38672</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343704</t>
+          <t>343937</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355038</t>
+          <t>354810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342663</t>
+          <t>343298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>359874</t>
+          <t>360229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>692057</t>
+          <t>691455</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>712546</t>
+          <t>712081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>9671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25255</t>
+          <t>25398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30421</t>
+          <t>31144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27594</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50099</t>
+          <t>50277</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178053</t>
+          <t>177910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193152</t>
+          <t>193637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177247</t>
+          <t>176524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194794</t>
+          <t>194865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>360877</t>
+          <t>360699</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383382</t>
+          <t>383893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>15314</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>16559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263949</t>
+          <t>264029</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263691</t>
+          <t>262830</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275011</t>
+          <t>275041</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>532742</t>
+          <t>532396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>544743</t>
+          <t>544687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24839</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46881</t>
+          <t>48426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25829</t>
+          <t>25619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50748</t>
+          <t>50048</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56333</t>
+          <t>55766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90120</t>
+          <t>88459</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>568146</t>
+          <t>566601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>590188</t>
+          <t>590280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>587471</t>
+          <t>588171</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>612390</t>
+          <t>612600</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1163126</t>
+          <t>1164787</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1196913</t>
+          <t>1197480</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,55%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>37190</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65154</t>
+          <t>65343</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57966</t>
+          <t>58610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92513</t>
+          <t>90984</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102901</t>
+          <t>101108</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>147305</t>
+          <t>146917</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>678641</t>
+          <t>678452</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>707730</t>
+          <t>706605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>690998</t>
+          <t>692527</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>725545</t>
+          <t>724901</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1380001</t>
+          <t>1380389</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1424405</t>
+          <t>1426198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>139518</t>
+          <t>140911</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>191126</t>
+          <t>188514</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>183046</t>
+          <t>185394</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>240842</t>
+          <t>242778</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>338131</t>
+          <t>341330</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>415727</t>
+          <t>414212</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3085417</t>
+          <t>3088029</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3137025</t>
+          <t>3135632</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3138355</t>
+          <t>3136419</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3196151</t>
+          <t>3193803</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6240014</t>
+          <t>6241529</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6317610</t>
+          <t>6314411</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36638</t>
+          <t>33500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50863</t>
+          <t>51985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46369</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76402</t>
+          <t>76856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258100</t>
+          <t>261238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279098</t>
+          <t>279654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236382</t>
+          <t>235260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261012</t>
+          <t>261078</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>505581</t>
+          <t>505127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>535614</t>
+          <t>535473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29429</t>
+          <t>29797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56083</t>
+          <t>56355</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31411</t>
+          <t>30092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57285</t>
+          <t>56474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65902</t>
+          <t>66820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102485</t>
+          <t>102490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449444</t>
+          <t>449172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476098</t>
+          <t>475730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466480</t>
+          <t>467291</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492354</t>
+          <t>493673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926807</t>
+          <t>926802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>963390</t>
+          <t>962472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15431</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>35644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18277</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>40573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39201</t>
+          <t>39022</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68985</t>
+          <t>67873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285861</t>
+          <t>288402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308615</t>
+          <t>308700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>302442</t>
+          <t>300447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322743</t>
+          <t>322338</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>596081</t>
+          <t>597193</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625865</t>
+          <t>626044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,13%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33689</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>51004</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45047</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75363</t>
+          <t>74686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340293</t>
+          <t>340970</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359986</t>
+          <t>360311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>338841</t>
+          <t>337947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362714</t>
+          <t>361962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>687570</t>
+          <t>688247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717886</t>
+          <t>717813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40280</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56656</t>
+          <t>55439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55739</t>
+          <t>57095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86310</t>
+          <t>89218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172338</t>
+          <t>172874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193730</t>
+          <t>194088</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162935</t>
+          <t>164152</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186354</t>
+          <t>187157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345899</t>
+          <t>342991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>376470</t>
+          <t>375114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24946</t>
+          <t>25462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21332</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42890</t>
+          <t>43441</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>36486</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62468</t>
+          <t>63000</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249035</t>
+          <t>248519</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265645</t>
+          <t>264793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>237141</t>
+          <t>236590</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258583</t>
+          <t>258699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491544</t>
+          <t>491012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>517895</t>
+          <t>517526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32638</t>
+          <t>31531</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61237</t>
+          <t>61540</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40490</t>
+          <t>39785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70030</t>
+          <t>71331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80491</t>
+          <t>80114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122694</t>
+          <t>122768</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>601551</t>
+          <t>601248</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>630150</t>
+          <t>631257</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>623823</t>
+          <t>622522</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>653363</t>
+          <t>654068</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1233947</t>
+          <t>1233873</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1276150</t>
+          <t>1276527</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>38214</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69261</t>
+          <t>66476</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67836</t>
+          <t>68143</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83803</t>
+          <t>82940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>125235</t>
+          <t>124259</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>709837</t>
+          <t>712622</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>740311</t>
+          <t>740884</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>756017</t>
+          <t>755710</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>785514</t>
+          <t>786195</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1477716</t>
+          <t>1478692</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1519148</t>
+          <t>1520011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>219117</t>
+          <t>222019</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>283385</t>
+          <t>282813</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>287725</t>
+          <t>289062</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>357100</t>
+          <t>360613</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>527507</t>
+          <t>527858</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>620899</t>
+          <t>621491</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3143394</t>
+          <t>3143966</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3207662</t>
+          <t>3204760</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3201209</t>
+          <t>3197696</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3270584</t>
+          <t>3269247</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6364189</t>
+          <t>6363597</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6457581</t>
+          <t>6457230</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25956</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>16042</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37409</t>
+          <t>37185</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>30178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58184</t>
+          <t>56388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267805</t>
+          <t>267520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284408</t>
+          <t>284251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251294</t>
+          <t>251518</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>271849</t>
+          <t>272661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524280</t>
+          <t>526076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>551724</t>
+          <t>552286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13099</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31792</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52039</t>
+          <t>52873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475370</t>
+          <t>476222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492379</t>
+          <t>492489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491292</t>
+          <t>491092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509985</t>
+          <t>510101</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>973620</t>
+          <t>972786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>997890</t>
+          <t>999209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>10602</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26512</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307394</t>
+          <t>307963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316750</t>
+          <t>316716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316291</t>
+          <t>316963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330061</t>
+          <t>330101</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628362</t>
+          <t>628308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645396</t>
+          <t>644728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>20707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43473</t>
+          <t>43209</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29607</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57998</t>
+          <t>56689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>56708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90877</t>
+          <t>94842</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>326491</t>
+          <t>326755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349124</t>
+          <t>349257</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>329285</t>
+          <t>330594</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357676</t>
+          <t>357678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>666370</t>
+          <t>662405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>699437</t>
+          <t>700539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>23659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187296</t>
+          <t>187562</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202347</t>
+          <t>202657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194735</t>
+          <t>193855</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209308</t>
+          <t>209559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386645</t>
+          <t>387364</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408594</t>
+          <t>409122</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31984</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>16389</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37067</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35810</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63264</t>
+          <t>63520</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231139</t>
+          <t>230956</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248493</t>
+          <t>249444</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236048</t>
+          <t>236749</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>257031</t>
+          <t>256726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>472974</t>
+          <t>472718</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500428</t>
+          <t>500383</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18115</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40920</t>
+          <t>38902</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29906</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56013</t>
+          <t>57012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53577</t>
+          <t>52955</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88169</t>
+          <t>87106</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>615638</t>
+          <t>617656</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638443</t>
+          <t>638926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>635281</t>
+          <t>634282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>660990</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1259683</t>
+          <t>1260746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1294275</t>
+          <t>1294897</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40279</t>
+          <t>40906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71019</t>
+          <t>69974</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47155</t>
+          <t>46632</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79259</t>
+          <t>79840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>97341</t>
+          <t>96610</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>142213</t>
+          <t>140599</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>707564</t>
+          <t>708609</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>738304</t>
+          <t>737677</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>746908</t>
+          <t>746327</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>779012</t>
+          <t>779535</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1462537</t>
+          <t>1464151</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1507409</t>
+          <t>1508140</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>161060</t>
+          <t>162097</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>215899</t>
+          <t>216780</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>214419</t>
+          <t>215180</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>275554</t>
+          <t>277386</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>392163</t>
+          <t>389233</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>478357</t>
+          <t>476535</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3178451</t>
+          <t>3177570</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3233290</t>
+          <t>3232253</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3268988</t>
+          <t>3267156</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3330123</t>
+          <t>3329362</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6460535</t>
+          <t>6462357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6546729</t>
+          <t>6549659</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20088</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41495</t>
+          <t>42738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23323</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38738</t>
+          <t>39202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48461</t>
+          <t>47477</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76328</t>
+          <t>74605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269948</t>
+          <t>268705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>291355</t>
+          <t>290907</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250897</t>
+          <t>250433</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266312</t>
+          <t>266485</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524749</t>
+          <t>526472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>552616</t>
+          <t>553600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69916</t>
+          <t>69082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110585</t>
+          <t>112625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66170</t>
+          <t>66383</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92657</t>
+          <t>92905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143239</t>
+          <t>143919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191931</t>
+          <t>192048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407805</t>
+          <t>405765</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>448474</t>
+          <t>449308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422312</t>
+          <t>422064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448799</t>
+          <t>448586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>841428</t>
+          <t>841311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>890120</t>
+          <t>889440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29368</t>
+          <t>30742</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52446</t>
+          <t>52772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29963</t>
+          <t>29278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49465</t>
+          <t>48267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64182</t>
+          <t>65019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93653</t>
+          <t>95668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>263604</t>
+          <t>263278</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286682</t>
+          <t>285308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>299663</t>
+          <t>300861</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319165</t>
+          <t>319850</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>571525</t>
+          <t>569510</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>600996</t>
+          <t>600159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>12366</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36233</t>
+          <t>35940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>28208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26502</t>
+          <t>25466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57600</t>
+          <t>57281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276324</t>
+          <t>276617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300054</t>
+          <t>300191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>446412</t>
+          <t>447510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465951</t>
+          <t>465431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>730674</t>
+          <t>730993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761772</t>
+          <t>762808</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19558</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25383</t>
+          <t>25760</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21117</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39870</t>
+          <t>41118</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159184</t>
+          <t>159367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170132</t>
+          <t>170487</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233396</t>
+          <t>233019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248810</t>
+          <t>248852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397651</t>
+          <t>396403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>416404</t>
+          <t>416062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46211</t>
+          <t>45864</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70928</t>
+          <t>69267</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41434</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61431</t>
+          <t>61752</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94138</t>
+          <t>93630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123895</t>
+          <t>123340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>198708</t>
+          <t>200369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223425</t>
+          <t>223772</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195625</t>
+          <t>195304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215622</t>
+          <t>215794</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>402797</t>
+          <t>403352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>432554</t>
+          <t>433062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54029</t>
+          <t>54389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86194</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104052</t>
+          <t>104734</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>538269</t>
+          <t>567236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>170580</t>
+          <t>166700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>794377</t>
+          <t>746560</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>538085</t>
+          <t>538804</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>570250</t>
+          <t>569890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310996</t>
+          <t>282029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>745213</t>
+          <t>744531</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>679167</t>
+          <t>726984</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1302964</t>
+          <t>1306844</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,69%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64356</t>
+          <t>64982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49245</t>
+          <t>49398</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73693</t>
+          <t>72076</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63338</t>
+          <t>66486</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127991</t>
+          <t>129953</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>864364</t>
+          <t>863738</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>910193</t>
+          <t>910864</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>644038</t>
+          <t>645655</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>668486</t>
+          <t>668333</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1518461</t>
+          <t>1516499</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1583114</t>
+          <t>1579966</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>288845</t>
+          <t>280643</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>406715</t>
+          <t>412039</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>390677</t>
+          <t>390238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1159719</t>
+          <t>1157341</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>739944</t>
+          <t>736831</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1622589</t>
+          <t>1507037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3053102</t>
+          <t>3047778</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3170972</t>
+          <t>3179174</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2552561</t>
+          <t>2554939</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3321603</t>
+          <t>3322042</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5549508</t>
+          <t>5665060</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6432153</t>
+          <t>6435266</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_fisi_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23574</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257124</t>
+          <t>257467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>269610</t>
+          <t>269487</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248302</t>
+          <t>247678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258778</t>
+          <t>258706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>510274</t>
+          <t>510058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>526374</t>
+          <t>525764</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52965</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50889</t>
+          <t>51643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61052</t>
+          <t>61600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95916</t>
+          <t>95175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>440110</t>
+          <t>439432</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>466222</t>
+          <t>464997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>453060</t>
+          <t>452306</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476478</t>
+          <t>475588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>901108</t>
+          <t>901849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935972</t>
+          <t>935424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25841</t>
+          <t>26253</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304184</t>
+          <t>304938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315788</t>
+          <t>315961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318636</t>
+          <t>318524</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331127</t>
+          <t>331035</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628417</t>
+          <t>628005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644986</t>
+          <t>644766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>28154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38672</t>
+          <t>38064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343937</t>
+          <t>343411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>354810</t>
+          <t>354913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343298</t>
+          <t>343302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360229</t>
+          <t>359930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691455</t>
+          <t>692063</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>712081</t>
+          <t>711461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25398</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>12623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31144</t>
+          <t>29947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27083</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>50789</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177910</t>
+          <t>177674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>193637</t>
+          <t>193144</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176524</t>
+          <t>177721</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194865</t>
+          <t>195045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>360699</t>
+          <t>360187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>383893</t>
+          <t>383616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6782</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264029</t>
+          <t>264040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262830</t>
+          <t>263451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275041</t>
+          <t>275051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>532396</t>
+          <t>532193</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>544687</t>
+          <t>544122</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48426</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25619</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50048</t>
+          <t>49213</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55766</t>
+          <t>55383</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88459</t>
+          <t>87543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>566601</t>
+          <t>566737</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>590280</t>
+          <t>590208</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>588171</t>
+          <t>589006</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>612600</t>
+          <t>612402</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1164787</t>
+          <t>1165703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1197480</t>
+          <t>1197863</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>36877</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>65343</t>
+          <t>64029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58610</t>
+          <t>57454</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90984</t>
+          <t>92491</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>101108</t>
+          <t>103760</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>146917</t>
+          <t>146074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>678452</t>
+          <t>679766</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>706605</t>
+          <t>706918</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>692527</t>
+          <t>691020</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>724901</t>
+          <t>726057</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1380389</t>
+          <t>1381232</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1426198</t>
+          <t>1423546</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>140911</t>
+          <t>138475</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>188514</t>
+          <t>189999</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>185394</t>
+          <t>182438</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>242778</t>
+          <t>241226</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>341330</t>
+          <t>338008</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>414212</t>
+          <t>411953</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3088029</t>
+          <t>3086544</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3135632</t>
+          <t>3138068</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3136419</t>
+          <t>3137971</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3193803</t>
+          <t>3196759</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6241529</t>
+          <t>6243788</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6314411</t>
+          <t>6317733</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26167</t>
+          <t>26578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51985</t>
+          <t>51303</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>46455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76856</t>
+          <t>77601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261238</t>
+          <t>261513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279654</t>
+          <t>279410</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235260</t>
+          <t>235942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>261078</t>
+          <t>260667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>505127</t>
+          <t>504382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>535473</t>
+          <t>535528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,02%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56355</t>
+          <t>55280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30092</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56474</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66820</t>
+          <t>67258</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102490</t>
+          <t>104901</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>449172</t>
+          <t>450247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>475730</t>
+          <t>477817</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467291</t>
+          <t>467165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493673</t>
+          <t>493935</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>926802</t>
+          <t>924391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>962472</t>
+          <t>962034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15346</t>
+          <t>16113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40573</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>37510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67873</t>
+          <t>67267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>288402</t>
+          <t>286552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308700</t>
+          <t>307933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300447</t>
+          <t>302559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322338</t>
+          <t>322369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>597193</t>
+          <t>597799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>626044</t>
+          <t>627556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>34878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26989</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51004</t>
+          <t>49438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>45333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74686</t>
+          <t>75829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340970</t>
+          <t>339104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360311</t>
+          <t>359125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>337947</t>
+          <t>339513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361962</t>
+          <t>363098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>688247</t>
+          <t>687104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>717813</t>
+          <t>717600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18530</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32434</t>
+          <t>32815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55439</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57095</t>
+          <t>56175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89218</t>
+          <t>87976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172874</t>
+          <t>173183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>194088</t>
+          <t>194276</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164152</t>
+          <t>162250</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187157</t>
+          <t>186776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>342991</t>
+          <t>344233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375114</t>
+          <t>376034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25462</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43441</t>
+          <t>44620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36486</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>62374</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248519</t>
+          <t>248055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264793</t>
+          <t>264615</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236590</t>
+          <t>235411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>258699</t>
+          <t>257342</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491012</t>
+          <t>491638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>517526</t>
+          <t>518475</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31531</t>
+          <t>31779</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61540</t>
+          <t>60408</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39785</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71331</t>
+          <t>69698</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80114</t>
+          <t>79514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122768</t>
+          <t>118563</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>601248</t>
+          <t>602380</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>631257</t>
+          <t>631009</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>622522</t>
+          <t>624155</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>654068</t>
+          <t>655341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1233873</t>
+          <t>1238078</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1276527</t>
+          <t>1277127</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38214</t>
+          <t>38014</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66476</t>
+          <t>67904</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37658</t>
+          <t>37207</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>67027</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82940</t>
+          <t>83321</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>124259</t>
+          <t>124097</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>712622</t>
+          <t>711194</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>740884</t>
+          <t>741084</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>755710</t>
+          <t>756826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>786195</t>
+          <t>786646</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1478692</t>
+          <t>1478854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1520011</t>
+          <t>1519630</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>222019</t>
+          <t>218116</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>282813</t>
+          <t>285421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>289062</t>
+          <t>287533</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>360613</t>
+          <t>360504</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>527858</t>
+          <t>527790</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>621491</t>
+          <t>627280</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3143966</t>
+          <t>3141358</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3204760</t>
+          <t>3208663</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3197696</t>
+          <t>3197805</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3269247</t>
+          <t>3270776</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6363597</t>
+          <t>6357808</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6457230</t>
+          <t>6457298</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26241</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37185</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56388</t>
+          <t>57782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267520</t>
+          <t>267536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>284251</t>
+          <t>283522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251518</t>
+          <t>253027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272661</t>
+          <t>272597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526076</t>
+          <t>524682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>552286</t>
+          <t>552276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12983</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31992</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>27048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52873</t>
+          <t>53080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476222</t>
+          <t>476015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492489</t>
+          <t>492233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>491092</t>
+          <t>489821</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510101</t>
+          <t>509459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>972786</t>
+          <t>972579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>999209</t>
+          <t>998611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>20504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26566</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307963</t>
+          <t>307826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316716</t>
+          <t>316317</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316963</t>
+          <t>315805</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>330101</t>
+          <t>330074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628308</t>
+          <t>629402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644728</t>
+          <t>644829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20707</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43209</t>
+          <t>42774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29605</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>56781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56708</t>
+          <t>56773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94842</t>
+          <t>92791</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>326755</t>
+          <t>327190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349257</t>
+          <t>348200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>330594</t>
+          <t>330502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>357678</t>
+          <t>356532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>662405</t>
+          <t>664456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>700539</t>
+          <t>700474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>24355</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24732</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>41634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187562</t>
+          <t>186866</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202657</t>
+          <t>202363</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193855</t>
+          <t>194871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209559</t>
+          <t>209509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387364</t>
+          <t>388174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409122</t>
+          <t>409038</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32167</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36366</t>
+          <t>37079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63520</t>
+          <t>62219</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230956</t>
+          <t>230753</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249444</t>
+          <t>248994</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236749</t>
+          <t>236036</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>256726</t>
+          <t>257169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>472718</t>
+          <t>474019</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500383</t>
+          <t>501574</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17632</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30304</t>
+          <t>29722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57012</t>
+          <t>56452</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52955</t>
+          <t>52651</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87106</t>
+          <t>87475</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>617656</t>
+          <t>615712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638926</t>
+          <t>637621</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>634282</t>
+          <t>634842</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>660990</t>
+          <t>661572</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1260746</t>
+          <t>1260377</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1294897</t>
+          <t>1295201</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40906</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69974</t>
+          <t>72456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46632</t>
+          <t>47378</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>79840</t>
+          <t>80242</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96610</t>
+          <t>96223</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>140599</t>
+          <t>139963</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>708609</t>
+          <t>706127</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>737677</t>
+          <t>737843</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>746327</t>
+          <t>745925</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>779535</t>
+          <t>778789</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1464151</t>
+          <t>1464787</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1508140</t>
+          <t>1508527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162097</t>
+          <t>163918</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>216780</t>
+          <t>217219</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>215180</t>
+          <t>213063</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>277386</t>
+          <t>274503</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>389233</t>
+          <t>392156</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>476535</t>
+          <t>470234</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3177570</t>
+          <t>3177131</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3232253</t>
+          <t>3230432</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3267156</t>
+          <t>3270039</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3329362</t>
+          <t>3331479</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6462357</t>
+          <t>6468658</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6549659</t>
+          <t>6546736</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29740</t>
+          <t>28164</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>39228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>31844</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>24468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39202</t>
+          <t>40435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>60328</t>
+          <t>60008</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47477</t>
+          <t>49183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74605</t>
+          <t>74423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>281703</t>
+          <t>290681</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268705</t>
+          <t>279617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>290907</t>
+          <t>299889</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>259047</t>
+          <t>284217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250433</t>
+          <t>275626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>266485</t>
+          <t>291593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>540749</t>
+          <t>574898</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526472</t>
+          <t>560483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>553600</t>
+          <t>585723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,25%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88648</t>
+          <t>90504</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69082</t>
+          <t>71280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112625</t>
+          <t>112656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79217</t>
+          <t>83225</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66383</t>
+          <t>69601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92905</t>
+          <t>97714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>167865</t>
+          <t>173729</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143919</t>
+          <t>152296</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>192048</t>
+          <t>199905</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>429742</t>
+          <t>440143</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>405765</t>
+          <t>417991</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449308</t>
+          <t>459367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>435752</t>
+          <t>463269</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422064</t>
+          <t>448780</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448586</t>
+          <t>476893</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>865494</t>
+          <t>903412</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>841311</t>
+          <t>877236</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>889440</t>
+          <t>924845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40240</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30742</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52772</t>
+          <t>50560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>38808</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>30341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48267</t>
+          <t>49468</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>78413</t>
+          <t>77307</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65019</t>
+          <t>63243</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95668</t>
+          <t>91158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>275810</t>
+          <t>277494</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>263278</t>
+          <t>265433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285308</t>
+          <t>285911</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>310955</t>
+          <t>317573</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>300861</t>
+          <t>306913</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>319850</t>
+          <t>326040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>586765</t>
+          <t>595068</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>569510</t>
+          <t>581217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>600159</t>
+          <t>609132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>25476</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>41162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>20067</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28208</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>45543</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25466</t>
+          <t>33755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57281</t>
+          <t>67224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>291328</t>
+          <t>347669</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276617</t>
+          <t>331983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300191</t>
+          <t>358144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>457482</t>
+          <t>401894</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447510</t>
+          <t>390119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465431</t>
+          <t>408601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>748809</t>
+          <t>749564</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>730993</t>
+          <t>727883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>762808</t>
+          <t>761352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25760</t>
+          <t>25568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>31341</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>27297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41118</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>165802</t>
+          <t>191532</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159367</t>
+          <t>185090</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170487</t>
+          <t>196621</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>240378</t>
+          <t>209110</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233019</t>
+          <t>203350</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248852</t>
+          <t>214090</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>406180</t>
+          <t>400642</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>396403</t>
+          <t>391000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>416062</t>
+          <t>407285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57024</t>
+          <t>56508</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45864</t>
+          <t>45251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69267</t>
+          <t>67817</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50501</t>
+          <t>51104</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>41393</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61752</t>
+          <t>60934</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>107525</t>
+          <t>107612</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93630</t>
+          <t>92857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123340</t>
+          <t>124244</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>212612</t>
+          <t>214199</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>202890</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>223772</t>
+          <t>225456</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>206555</t>
+          <t>212646</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195304</t>
+          <t>202816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>215794</t>
+          <t>222357</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>419167</t>
+          <t>426845</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>403352</t>
+          <t>410213</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>433062</t>
+          <t>441600</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>69020</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>66013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85475</t>
+          <t>102749</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>288552</t>
+          <t>109955</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104734</t>
+          <t>93604</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>567236</t>
+          <t>128612</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>357572</t>
+          <t>191531</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166700</t>
+          <t>167835</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>746560</t>
+          <t>217294</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>555259</t>
+          <t>638111</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>538804</t>
+          <t>616938</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>569890</t>
+          <t>653674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>560713</t>
+          <t>662102</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>282029</t>
+          <t>643445</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>744531</t>
+          <t>678453</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1115972</t>
+          <t>1300213</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>726984</t>
+          <t>1274450</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1306844</t>
+          <t>1323909</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,75%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>43150</t>
+          <t>48815</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>37326</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64982</t>
+          <t>64818</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>60441</t>
+          <t>72606</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49398</t>
+          <t>59585</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72076</t>
+          <t>87933</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>103591</t>
+          <t>121421</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66486</t>
+          <t>101961</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>129953</t>
+          <t>142630</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>885570</t>
+          <t>749257</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>863738</t>
+          <t>733254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>910864</t>
+          <t>760746</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>657290</t>
+          <t>758725</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>645655</t>
+          <t>743398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>668333</t>
+          <t>771746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1542861</t>
+          <t>1507982</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1516499</t>
+          <t>1486773</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1579966</t>
+          <t>1527442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>361991</t>
+          <t>383676</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>280643</t>
+          <t>346484</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>412039</t>
+          <t>422103</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>584109</t>
+          <t>427416</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>390238</t>
+          <t>398113</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1157341</t>
+          <t>463994</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>946100</t>
+          <t>811091</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>736831</t>
+          <t>764914</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1507037</t>
+          <t>862677</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3097826</t>
+          <t>3149086</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3047778</t>
+          <t>3110659</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3179174</t>
+          <t>3186278</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3128171</t>
+          <t>3309538</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2554939</t>
+          <t>3272960</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3322042</t>
+          <t>3338841</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6225997</t>
+          <t>6458625</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5665060</t>
+          <t>6407039</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6435266</t>
+          <t>6504802</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_fisi_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
